--- a/downloads/data/chests.xlsx
+++ b/downloads/data/chests.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chest Data" sheetId="1" r:id="R5fc5b9da4a764a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chest Data" sheetId="1" r:id="R5ff479e667cc4949"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -261,27 +261,27 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="15" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="12.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="11.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -431,10 +431,10 @@
       <x:c r="G4"/>
       <x:c r="H4"/>
       <x:c r="I4" t="n">
-        <x:v>6.1</x:v>
+        <x:v>6.1000000000000005</x:v>
       </x:c>
       <x:c r="J4" t="n">
-        <x:v>15.075</x:v>
+        <x:v>15.075000000000001</x:v>
       </x:c>
       <x:c r="K4"/>
       <x:c r="L4" t="n">
@@ -466,7 +466,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>5.7</x:v>
+        <x:v>5.699999999999999</x:v>
       </x:c>
       <x:c r="F5"/>
       <x:c r="G5"/>
@@ -529,7 +529,7 @@
       <x:c r="Q6"/>
       <x:c r="R6"/>
       <x:c r="S6" t="n">
-        <x:v>29.7</x:v>
+        <x:v>29.699999999999996</x:v>
       </x:c>
       <x:c r="T6"/>
       <x:c r="U6"/>
@@ -686,16 +686,16 @@
         <x:v>35750</x:v>
       </x:c>
       <x:c r="M11" t="n">
-        <x:v>29204.545454545</x:v>
+        <x:v>29204.545454545456</x:v>
       </x:c>
       <x:c r="N11" t="n">
-        <x:v>17727.272727273</x:v>
+        <x:v>17727.272727272728</x:v>
       </x:c>
       <x:c r="O11" t="n">
-        <x:v>38863.636363636</x:v>
+        <x:v>38863.63636363636</x:v>
       </x:c>
       <x:c r="P11" t="n">
-        <x:v>43238.636363636</x:v>
+        <x:v>43238.63636363636</x:v>
       </x:c>
       <x:c r="Q11" t="n">
         <x:v>0.1607</x:v>
@@ -827,7 +827,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>54.3</x:v>
+        <x:v>54.300000000000004</x:v>
       </x:c>
       <x:c r="G15"/>
       <x:c r="H15"/>
@@ -841,19 +841,19 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c r="N15" t="n">
-        <x:v>117605.633802817</x:v>
+        <x:v>117605.6338028169</x:v>
       </x:c>
       <x:c r="O15" t="n">
-        <x:v>113380.281690141</x:v>
+        <x:v>113380.28169014085</x:v>
       </x:c>
       <x:c r="P15" t="n">
-        <x:v>167605.633802817</x:v>
+        <x:v>167605.6338028169</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>0.349295775</x:v>
+        <x:v>0.3492957746478873</x:v>
       </x:c>
       <x:c r="R15" t="n">
-        <x:v>0.076056338</x:v>
+        <x:v>0.07605633802816901</x:v>
       </x:c>
       <x:c r="S15" t="n">
         <x:v>85</x:v>
@@ -886,25 +886,25 @@
       <x:c r="J16"/>
       <x:c r="K16"/>
       <x:c r="L16" t="n">
-        <x:v>253625</x:v>
+        <x:v>253624.99999999997</x:v>
       </x:c>
       <x:c r="M16" t="n">
-        <x:v>387359.198998748</x:v>
+        <x:v>387359.19899874844</x:v>
       </x:c>
       <x:c r="N16" t="n">
-        <x:v>480600.750938673</x:v>
+        <x:v>480600.7509386733</x:v>
       </x:c>
       <x:c r="O16" t="n">
-        <x:v>419899.874843554</x:v>
+        <x:v>419899.87484355445</x:v>
       </x:c>
       <x:c r="P16" t="n">
-        <x:v>275344.180225282</x:v>
+        <x:v>275344.1802252816</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>0.683510638</x:v>
+        <x:v>0.6835106382978723</x:v>
       </x:c>
       <x:c r="R16" t="n">
-        <x:v>0.137359199</x:v>
+        <x:v>0.13735919899874843</x:v>
       </x:c>
       <x:c r="S16" t="n">
         <x:v>140</x:v>
@@ -971,22 +971,22 @@
         <x:v>79200</x:v>
       </x:c>
       <x:c r="M18" t="n">
-        <x:v>47619.047619048</x:v>
+        <x:v>47619.04761904762</x:v>
       </x:c>
       <x:c r="N18" t="n">
-        <x:v>50595.238095238</x:v>
+        <x:v>50595.23809523809</x:v>
       </x:c>
       <x:c r="O18" t="n">
-        <x:v>56547.619047619</x:v>
+        <x:v>56547.619047619046</x:v>
       </x:c>
       <x:c r="P18" t="n">
-        <x:v>66964.285714286</x:v>
+        <x:v>66964.28571428571</x:v>
       </x:c>
       <x:c r="Q18" t="n">
-        <x:v>1.017857143</x:v>
+        <x:v>1.0178571428571428</x:v>
       </x:c>
       <x:c r="R18" t="n">
-        <x:v>0.052327381</x:v>
+        <x:v>0.05232738095238095</x:v>
       </x:c>
       <x:c r="S18" t="n">
         <x:v>70</x:v>
@@ -1022,22 +1022,22 @@
         <x:v>90350</x:v>
       </x:c>
       <x:c r="M19" t="n">
-        <x:v>87726.523887974</x:v>
+        <x:v>87726.52388797364</x:v>
       </x:c>
       <x:c r="N19" t="n">
-        <x:v>95963.756177924</x:v>
+        <x:v>95963.75617792422</x:v>
       </x:c>
       <x:c r="O19" t="n">
-        <x:v>74958.81383855</x:v>
+        <x:v>74958.81383855025</x:v>
       </x:c>
       <x:c r="P19" t="n">
-        <x:v>96375.617792422</x:v>
+        <x:v>96375.61779242175</x:v>
       </x:c>
       <x:c r="Q19" t="n">
-        <x:v>2.212520593</x:v>
+        <x:v>2.212520593080725</x:v>
       </x:c>
       <x:c r="R19" t="n">
-        <x:v>0.103171334</x:v>
+        <x:v>0.10317133443163097</x:v>
       </x:c>
       <x:c r="S19" t="n">
         <x:v>140</x:v>
@@ -1073,22 +1073,22 @@
         <x:v>98000</x:v>
       </x:c>
       <x:c r="M20" t="n">
-        <x:v>148006.785411366</x:v>
+        <x:v>148006.78541136556</x:v>
       </x:c>
       <x:c r="N20" t="n">
-        <x:v>121713.316369805</x:v>
+        <x:v>121713.31636980492</x:v>
       </x:c>
       <x:c r="O20" t="n">
-        <x:v>150551.314673452</x:v>
+        <x:v>150551.31467345209</x:v>
       </x:c>
       <x:c r="P20" t="n">
-        <x:v>110687.022900763</x:v>
+        <x:v>110687.02290076336</x:v>
       </x:c>
       <x:c r="Q20" t="n">
-        <x:v>2.802374894</x:v>
+        <x:v>2.8023748939779476</x:v>
       </x:c>
       <x:c r="R20" t="n">
-        <x:v>0.127226463</x:v>
+        <x:v>0.1272264631043257</x:v>
       </x:c>
       <x:c r="S20" t="n">
         <x:v>140</x:v>
@@ -1124,22 +1124,22 @@
         <x:v>152150</x:v>
       </x:c>
       <x:c r="M21" t="n">
-        <x:v>124321.880650995</x:v>
+        <x:v>124321.88065099457</x:v>
       </x:c>
       <x:c r="N21" t="n">
-        <x:v>160036.16636528</x:v>
+        <x:v>160036.16636528028</x:v>
       </x:c>
       <x:c r="O21" t="n">
-        <x:v>164556.962025316</x:v>
+        <x:v>164556.96202531646</x:v>
       </x:c>
       <x:c r="P21" t="n">
-        <x:v>122513.56238698</x:v>
+        <x:v>122513.5623869801</x:v>
       </x:c>
       <x:c r="Q21" t="n">
-        <x:v>3.389692586</x:v>
+        <x:v>3.3896925858951175</x:v>
       </x:c>
       <x:c r="R21" t="n">
-        <x:v>0.169981917</x:v>
+        <x:v>0.16998191681735986</x:v>
       </x:c>
       <x:c r="S21" t="n">
         <x:v>150</x:v>
@@ -1223,10 +1223,10 @@
         <x:v>1190</x:v>
       </x:c>
       <x:c r="E24" t="n">
-        <x:v>35.1</x:v>
+        <x:v>35.099999999999994</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>100.2</x:v>
+        <x:v>100.19999999999999</x:v>
       </x:c>
       <x:c r="G24"/>
       <x:c r="H24"/>
@@ -1265,7 +1265,7 @@
         <x:v>87.3</x:v>
       </x:c>
       <x:c r="F25" t="n">
-        <x:v>152.4</x:v>
+        <x:v>152.39999999999998</x:v>
       </x:c>
       <x:c r="G25"/>
       <x:c r="H25"/>
@@ -1301,7 +1301,7 @@
         <x:v>2368</x:v>
       </x:c>
       <x:c r="E26" t="n">
-        <x:v>182.1</x:v>
+        <x:v>182.10000000000002</x:v>
       </x:c>
       <x:c r="F26" t="n">
         <x:v>202.8</x:v>
@@ -1315,22 +1315,22 @@
         <x:v>115950</x:v>
       </x:c>
       <x:c r="M26" t="n">
-        <x:v>70117.955439056</x:v>
+        <x:v>70117.95543905636</x:v>
       </x:c>
       <x:c r="N26" t="n">
-        <x:v>81258.191349934</x:v>
+        <x:v>81258.19134993447</x:v>
       </x:c>
       <x:c r="O26" t="n">
-        <x:v>156618.610747051</x:v>
+        <x:v>156618.6107470511</x:v>
       </x:c>
       <x:c r="P26" t="n">
-        <x:v>91087.811271298</x:v>
+        <x:v>91087.81127129751</x:v>
       </x:c>
       <x:c r="Q26" t="n">
-        <x:v>2.75491481</x:v>
+        <x:v>2.7549148099606815</x:v>
       </x:c>
       <x:c r="R26" t="n">
-        <x:v>0.132372215</x:v>
+        <x:v>0.13237221494102228</x:v>
       </x:c>
       <x:c r="S26" t="n">
         <x:v>140</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>3003</x:v>
       </x:c>
       <x:c r="E27" t="n">
-        <x:v>385.2</x:v>
+        <x:v>385.20000000000005</x:v>
       </x:c>
       <x:c r="F27" t="n">
         <x:v>256.8</x:v>
@@ -1366,22 +1366,22 @@
         <x:v>136100</x:v>
       </x:c>
       <x:c r="M27" t="n">
-        <x:v>139274.518584863</x:v>
+        <x:v>139274.5185848634</x:v>
       </x:c>
       <x:c r="N27" t="n">
-        <x:v>147111.509180475</x:v>
+        <x:v>147111.5091804747</x:v>
       </x:c>
       <x:c r="O27" t="n">
-        <x:v>163681.146439767</x:v>
+        <x:v>163681.14643976712</x:v>
       </x:c>
       <x:c r="P27" t="n">
-        <x:v>136363.636363636</x:v>
+        <x:v>136363.63636363635</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>3.377966861</x:v>
+        <x:v>3.3779668607254814</x:v>
       </x:c>
       <x:c r="R27" t="n">
-        <x:v>0.160770264</x:v>
+        <x:v>0.16077026421854007</x:v>
       </x:c>
       <x:c r="S27" t="n">
         <x:v>150</x:v>
@@ -1446,24 +1446,24 @@
       </x:c>
       <x:c r="D29"/>
       <x:c r="E29" t="n">
-        <x:v>381.180400891</x:v>
+        <x:v>381.1804008908686</x:v>
       </x:c>
       <x:c r="F29" t="n">
-        <x:v>426.169265033</x:v>
+        <x:v>426.16926503340756</x:v>
       </x:c>
       <x:c r="G29"/>
       <x:c r="H29"/>
       <x:c r="I29" t="n">
-        <x:v>38.398663697</x:v>
+        <x:v>38.39866369710467</x:v>
       </x:c>
       <x:c r="J29" t="n">
-        <x:v>56.054565702</x:v>
+        <x:v>56.05456570155902</x:v>
       </x:c>
       <x:c r="K29" t="n">
-        <x:v>560.356347439</x:v>
+        <x:v>560.3563474387528</x:v>
       </x:c>
       <x:c r="L29" t="n">
-        <x:v>306013.363028953</x:v>
+        <x:v>306013.3630289532</x:v>
       </x:c>
       <x:c r="M29"/>
       <x:c r="N29"/>
@@ -1472,10 +1472,10 @@
       <x:c r="Q29"/>
       <x:c r="R29"/>
       <x:c r="S29" t="n">
-        <x:v>280.757238307</x:v>
+        <x:v>280.75723830734967</x:v>
       </x:c>
       <x:c r="T29" t="n">
-        <x:v>0.093541203</x:v>
+        <x:v>0.0935412026726058</x:v>
       </x:c>
       <x:c r="U29"/>
     </x:row>
@@ -1491,15 +1491,15 @@
       </x:c>
       <x:c r="D30"/>
       <x:c r="E30" t="n">
-        <x:v>423.666666667</x:v>
+        <x:v>423.6666666666667</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>407.666666667</x:v>
+        <x:v>407.6666666666667</x:v>
       </x:c>
       <x:c r="G30"/>
       <x:c r="H30"/>
       <x:c r="I30" t="n">
-        <x:v>37.566666667</x:v>
+        <x:v>37.56666666666667</x:v>
       </x:c>
       <x:c r="J30" t="n">
         <x:v>52.36</x:v>
@@ -1517,10 +1517,10 @@
       <x:c r="Q30"/>
       <x:c r="R30"/>
       <x:c r="S30" t="n">
-        <x:v>279.155555556</x:v>
+        <x:v>279.15555555555557</x:v>
       </x:c>
       <x:c r="T30" t="n">
-        <x:v>0.109111111</x:v>
+        <x:v>0.10911111111111112</x:v>
       </x:c>
       <x:c r="U30"/>
     </x:row>
@@ -1626,24 +1626,24 @@
       </x:c>
       <x:c r="D33"/>
       <x:c r="E33" t="n">
-        <x:v>946.561326253</x:v>
+        <x:v>946.561326253076</x:v>
       </x:c>
       <x:c r="F33" t="n">
-        <x:v>913.404999352</x:v>
+        <x:v>913.4049993524155</x:v>
       </x:c>
       <x:c r="G33"/>
       <x:c r="H33"/>
       <x:c r="I33" t="n">
-        <x:v>149.016966714</x:v>
+        <x:v>149.0169667141562</x:v>
       </x:c>
       <x:c r="J33" t="n">
-        <x:v>227.513275482</x:v>
+        <x:v>227.51327548245047</x:v>
       </x:c>
       <x:c r="K33" t="n">
-        <x:v>1571.920735656</x:v>
+        <x:v>1571.9207356560032</x:v>
       </x:c>
       <x:c r="L33" t="n">
-        <x:v>852046.3670509</x:v>
+        <x:v>852046.3670509001</x:v>
       </x:c>
       <x:c r="M33"/>
       <x:c r="N33"/>
@@ -1652,10 +1652,10 @@
       <x:c r="Q33"/>
       <x:c r="R33"/>
       <x:c r="S33" t="n">
-        <x:v>1244.657427794</x:v>
+        <x:v>1244.657427794327</x:v>
       </x:c>
       <x:c r="T33" t="n">
-        <x:v>0.327289211</x:v>
+        <x:v>0.3272892112420671</x:v>
       </x:c>
       <x:c r="U33"/>
     </x:row>
@@ -1671,21 +1671,21 @@
       </x:c>
       <x:c r="D34"/>
       <x:c r="E34" t="n">
-        <x:v>4617.391304348</x:v>
+        <x:v>4617.391304347826</x:v>
       </x:c>
       <x:c r="F34" t="n">
-        <x:v>4095.652173913</x:v>
+        <x:v>4095.6521739130435</x:v>
       </x:c>
       <x:c r="G34"/>
       <x:c r="H34"/>
       <x:c r="I34" t="n">
-        <x:v>803.47826087</x:v>
+        <x:v>803.4782608695652</x:v>
       </x:c>
       <x:c r="J34" t="n">
-        <x:v>1164.057971014</x:v>
+        <x:v>1164.0579710144928</x:v>
       </x:c>
       <x:c r="K34" t="n">
-        <x:v>5238.260869565</x:v>
+        <x:v>5238.260869565217</x:v>
       </x:c>
       <x:c r="L34" t="n">
         <x:v>4130434.782608696</x:v>
@@ -1697,10 +1697,10 @@
       <x:c r="Q34"/>
       <x:c r="R34"/>
       <x:c r="S34" t="n">
-        <x:v>6513.043478261</x:v>
+        <x:v>6513.04347826087</x:v>
       </x:c>
       <x:c r="T34" t="n">
-        <x:v>1.007246377</x:v>
+        <x:v>1.0072463768115942</x:v>
       </x:c>
       <x:c r="U34"/>
     </x:row>
@@ -1718,45 +1718,45 @@
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E35" t="n">
-        <x:v>2044.887780549</x:v>
+        <x:v>2044.8877805486284</x:v>
       </x:c>
       <x:c r="F35"/>
       <x:c r="G35" t="n">
-        <x:v>0.144222776</x:v>
+        <x:v>0.14422277639235245</x:v>
       </x:c>
       <x:c r="H35" t="n">
-        <x:v>0.100997506</x:v>
+        <x:v>0.10099750623441396</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:v>962.177888612</x:v>
+        <x:v>962.1778886118038</x:v>
       </x:c>
       <x:c r="J35" t="n">
-        <x:v>978.802992519</x:v>
+        <x:v>978.8029925187031</x:v>
       </x:c>
       <x:c r="K35" t="n">
-        <x:v>1577.306733167</x:v>
+        <x:v>1577.3067331670823</x:v>
       </x:c>
       <x:c r="L35" t="n">
-        <x:v>206151.288445553</x:v>
+        <x:v>206151.28844555275</x:v>
       </x:c>
       <x:c r="M35" t="n">
-        <x:v>349127.182044888</x:v>
+        <x:v>349127.18204488774</x:v>
       </x:c>
       <x:c r="N35" t="n">
-        <x:v>336658.354114713</x:v>
+        <x:v>336658.3541147132</x:v>
       </x:c>
       <x:c r="O35" t="n">
-        <x:v>396924.355777224</x:v>
+        <x:v>396924.3557772236</x:v>
       </x:c>
       <x:c r="P35"/>
       <x:c r="Q35" t="n">
-        <x:v>0.885286783</x:v>
+        <x:v>0.8852867830423939</x:v>
       </x:c>
       <x:c r="R35" t="n">
-        <x:v>0.39276808</x:v>
+        <x:v>0.39276807980049877</x:v>
       </x:c>
       <x:c r="S35" t="n">
-        <x:v>3345.802161264</x:v>
+        <x:v>3345.802161263508</x:v>
       </x:c>
       <x:c r="T35"/>
       <x:c r="U35"/>
@@ -1775,45 +1775,45 @@
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E36" t="n">
-        <x:v>2201.834862385</x:v>
+        <x:v>2201.8348623853212</x:v>
       </x:c>
       <x:c r="F36"/>
       <x:c r="G36" t="n">
-        <x:v>0.139063254</x:v>
+        <x:v>0.13906325446644133</x:v>
       </x:c>
       <x:c r="H36" t="n">
-        <x:v>0.09464027</x:v>
+        <x:v>0.09464027040077258</x:v>
       </x:c>
       <x:c r="I36" t="n">
-        <x:v>808.788025109</x:v>
+        <x:v>808.7880251086432</x:v>
       </x:c>
       <x:c r="J36" t="n">
-        <x:v>1042.974408498</x:v>
+        <x:v>1042.97440849831</x:v>
       </x:c>
       <x:c r="K36" t="n">
-        <x:v>1441.332689522</x:v>
+        <x:v>1441.3326895219702</x:v>
       </x:c>
       <x:c r="L36" t="n">
-        <x:v>202076.291646548</x:v>
+        <x:v>202076.2916465476</x:v>
       </x:c>
       <x:c r="M36" t="n">
-        <x:v>381458.232737808</x:v>
+        <x:v>381458.23273780785</x:v>
       </x:c>
       <x:c r="N36" t="n">
-        <x:v>357315.306615162</x:v>
+        <x:v>357315.3066151617</x:v>
       </x:c>
       <x:c r="O36" t="n">
-        <x:v>357315.306615162</x:v>
+        <x:v>357315.3066151617</x:v>
       </x:c>
       <x:c r="P36"/>
       <x:c r="Q36" t="n">
-        <x:v>1.07194592</x:v>
+        <x:v>1.0719459198454853</x:v>
       </x:c>
       <x:c r="R36" t="n">
-        <x:v>0.351521004</x:v>
+        <x:v>0.3515210043457267</x:v>
       </x:c>
       <x:c r="S36" t="n">
-        <x:v>3887.011105746</x:v>
+        <x:v>3887.0111057460167</x:v>
       </x:c>
       <x:c r="T36"/>
       <x:c r="U36"/>
@@ -1832,45 +1832,45 @@
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E37" t="n">
-        <x:v>2453.102453102</x:v>
+        <x:v>2453.102453102453</x:v>
       </x:c>
       <x:c r="F37"/>
       <x:c r="G37" t="n">
-        <x:v>0.13461142</x:v>
+        <x:v>0.13461142032570603</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>0.097093383</x:v>
+        <x:v>0.09709338280766852</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:v>828.695114409</x:v>
+        <x:v>828.6951144094</x:v>
       </x:c>
       <x:c r="J37" t="n">
-        <x:v>1060.606060606</x:v>
+        <x:v>1060.6060606060605</x:v>
       </x:c>
       <x:c r="K37" t="n">
-        <x:v>1296.639868068</x:v>
+        <x:v>1296.6398680684397</x:v>
       </x:c>
       <x:c r="L37" t="n">
-        <x:v>208616.780045351</x:v>
+        <x:v>208616.78004535148</x:v>
       </x:c>
       <x:c r="M37" t="n">
-        <x:v>366934.652648938</x:v>
+        <x:v>366934.65264893835</x:v>
       </x:c>
       <x:c r="N37" t="n">
-        <x:v>360750.360750361</x:v>
+        <x:v>360750.3607503607</x:v>
       </x:c>
       <x:c r="O37" t="n">
-        <x:v>359719.645433931</x:v>
+        <x:v>359719.64543393115</x:v>
       </x:c>
       <x:c r="P37"/>
       <x:c r="Q37" t="n">
-        <x:v>0.933828077</x:v>
+        <x:v>0.9338280766852196</x:v>
       </x:c>
       <x:c r="R37" t="n">
-        <x:v>0.395382395</x:v>
+        <x:v>0.3953823953823954</x:v>
       </x:c>
       <x:c r="S37" t="n">
-        <x:v>3267.367553082</x:v>
+        <x:v>3267.3675530818387</x:v>
       </x:c>
       <x:c r="T37"/>
       <x:c r="U37"/>
@@ -1883,51 +1883,51 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>BASILISK</x:v>
+        <x:v>ASHEN</x:v>
       </x:c>
       <x:c r="D38" t="n">
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E38" t="n">
-        <x:v>2353.823088456</x:v>
+        <x:v>2302.0361990950223</x:v>
       </x:c>
       <x:c r="F38"/>
       <x:c r="G38" t="n">
-        <x:v>0.137931034</x:v>
+        <x:v>0.13829185520361992</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>0.086956522</x:v>
+        <x:v>0.09869909502262443</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:v>787.106446777</x:v>
+        <x:v>830.0339366515838</x:v>
       </x:c>
       <x:c r="J38" t="n">
-        <x:v>955.772113943</x:v>
+        <x:v>1035.0678733031675</x:v>
       </x:c>
       <x:c r="K38" t="n">
-        <x:v>1330.584707646</x:v>
+        <x:v>1391.4027149321269</x:v>
       </x:c>
       <x:c r="L38" t="n">
-        <x:v>197151.424287856</x:v>
+        <x:v>192449.09502262442</x:v>
       </x:c>
       <x:c r="M38" t="n">
-        <x:v>397301.349325337</x:v>
+        <x:v>398755.65610859724</x:v>
       </x:c>
       <x:c r="N38" t="n">
-        <x:v>363568.215892054</x:v>
+        <x:v>404411.76470588235</x:v>
       </x:c>
       <x:c r="O38" t="n">
-        <x:v>404797.6011994</x:v>
+        <x:v>335124.4343891403</x:v>
       </x:c>
       <x:c r="P38"/>
       <x:c r="Q38" t="n">
-        <x:v>1.124437781</x:v>
+        <x:v>0.9417420814479638</x:v>
       </x:c>
       <x:c r="R38" t="n">
-        <x:v>0.362068966</x:v>
+        <x:v>0.40384615384615385</x:v>
       </x:c>
       <x:c r="S38" t="n">
-        <x:v>3598.20089955</x:v>
+        <x:v>3068.438914027149</x:v>
       </x:c>
       <x:c r="T38"/>
       <x:c r="U38"/>
@@ -1940,51 +1940,51 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>BRIAREUS</x:v>
+        <x:v>BASILISK</x:v>
       </x:c>
       <x:c r="D39" t="n">
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E39" t="n">
-        <x:v>2350.698856417</x:v>
+        <x:v>2353.823088455772</x:v>
       </x:c>
       <x:c r="F39"/>
       <x:c r="G39" t="n">
-        <x:v>0.130559085</x:v>
+        <x:v>0.13793103448275862</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>0.081003812</x:v>
+        <x:v>0.08695652173913043</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:v>860.864040661</x:v>
+        <x:v>787.1064467766117</x:v>
       </x:c>
       <x:c r="J39" t="n">
-        <x:v>1053.049555273</x:v>
+        <x:v>955.7721139430284</x:v>
       </x:c>
       <x:c r="K39" t="n">
-        <x:v>1469.18678526</x:v>
+        <x:v>1330.5847076461769</x:v>
       </x:c>
       <x:c r="L39" t="n">
-        <x:v>198697.585768742</x:v>
+        <x:v>197151.4242878561</x:v>
       </x:c>
       <x:c r="M39" t="n">
-        <x:v>406607.369758577</x:v>
+        <x:v>397301.34932533733</x:v>
       </x:c>
       <x:c r="N39" t="n">
-        <x:v>358958.068614994</x:v>
+        <x:v>363568.21589205397</x:v>
       </x:c>
       <x:c r="O39" t="n">
-        <x:v>371664.548919949</x:v>
+        <x:v>404797.60119940026</x:v>
       </x:c>
       <x:c r="P39"/>
       <x:c r="Q39" t="n">
-        <x:v>1.24841169</x:v>
+        <x:v>1.1244377811094453</x:v>
       </x:c>
       <x:c r="R39" t="n">
-        <x:v>0.413595934</x:v>
+        <x:v>0.3620689655172414</x:v>
       </x:c>
       <x:c r="S39" t="n">
-        <x:v>3144.853875476</x:v>
+        <x:v>3598.2008995502247</x:v>
       </x:c>
       <x:c r="T39"/>
       <x:c r="U39"/>
@@ -1997,51 +1997,51 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>DOOMSDAY</x:v>
+        <x:v>BRIAREUS</x:v>
       </x:c>
       <x:c r="D40" t="n">
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E40" t="n">
-        <x:v>2178.272980501</x:v>
+        <x:v>2350.6988564167723</x:v>
       </x:c>
       <x:c r="F40"/>
       <x:c r="G40" t="n">
-        <x:v>0.13816156</x:v>
+        <x:v>0.13055908513341805</x:v>
       </x:c>
       <x:c r="H40" t="n">
-        <x:v>0.091086351</x:v>
+        <x:v>0.08100381194409148</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:v>830.08356546</x:v>
+        <x:v>860.864040660737</x:v>
       </x:c>
       <x:c r="J40" t="n">
-        <x:v>1132.311977716</x:v>
+        <x:v>1053.0495552731893</x:v>
       </x:c>
       <x:c r="K40" t="n">
-        <x:v>1461.002785515</x:v>
+        <x:v>1469.1867852604828</x:v>
       </x:c>
       <x:c r="L40" t="n">
-        <x:v>201392.757660167</x:v>
+        <x:v>198697.58576874208</x:v>
       </x:c>
       <x:c r="M40" t="n">
-        <x:v>391364.902506964</x:v>
+        <x:v>406607.3697585769</x:v>
       </x:c>
       <x:c r="N40" t="n">
-        <x:v>359331.47632312</x:v>
+        <x:v>358958.06861499365</x:v>
       </x:c>
       <x:c r="O40" t="n">
-        <x:v>377437.325905292</x:v>
+        <x:v>371664.54891994916</x:v>
       </x:c>
       <x:c r="P40"/>
       <x:c r="Q40" t="n">
-        <x:v>0.969359331</x:v>
+        <x:v>1.2484116899618807</x:v>
       </x:c>
       <x:c r="R40" t="n">
-        <x:v>0.378272981</x:v>
+        <x:v>0.4135959339263024</x:v>
       </x:c>
       <x:c r="S40" t="n">
-        <x:v>3649.025069638</x:v>
+        <x:v>3144.8538754764927</x:v>
       </x:c>
       <x:c r="T40"/>
       <x:c r="U40"/>
@@ -2054,51 +2054,51 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>HELLFORGE</x:v>
+        <x:v>DOOMSDAY</x:v>
       </x:c>
       <x:c r="D41" t="n">
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E41" t="n">
-        <x:v>2200.180342651</x:v>
+        <x:v>2178.272980501393</x:v>
       </x:c>
       <x:c r="F41"/>
       <x:c r="G41" t="n">
-        <x:v>0.140667268</x:v>
+        <x:v>0.1381615598885794</x:v>
       </x:c>
       <x:c r="H41" t="n">
-        <x:v>0.100090171</x:v>
+        <x:v>0.09108635097493037</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:v>811.541929666</x:v>
+        <x:v>830.0835654596101</x:v>
       </x:c>
       <x:c r="J41" t="n">
-        <x:v>1190.261496844</x:v>
+        <x:v>1132.3119777158774</x:v>
       </x:c>
       <x:c r="K41" t="n">
-        <x:v>1519.386834986</x:v>
+        <x:v>1461.0027855153203</x:v>
       </x:c>
       <x:c r="L41" t="n">
-        <x:v>196798.917944094</x:v>
+        <x:v>201392.75766016715</x:v>
       </x:c>
       <x:c r="M41" t="n">
-        <x:v>308836.789900812</x:v>
+        <x:v>391364.90250696376</x:v>
       </x:c>
       <x:c r="N41" t="n">
-        <x:v>340396.753832281</x:v>
+        <x:v>359331.4763231198</x:v>
       </x:c>
       <x:c r="O41" t="n">
-        <x:v>358431.018935978</x:v>
+        <x:v>377437.32590529247</x:v>
       </x:c>
       <x:c r="P41"/>
       <x:c r="Q41" t="n">
-        <x:v>1.04147881</x:v>
+        <x:v>0.9693593314763231</x:v>
       </x:c>
       <x:c r="R41" t="n">
-        <x:v>0.400811542</x:v>
+        <x:v>0.37827298050139274</x:v>
       </x:c>
       <x:c r="S41" t="n">
-        <x:v>3742.110009017</x:v>
+        <x:v>3649.025069637883</x:v>
       </x:c>
       <x:c r="T41"/>
       <x:c r="U41"/>
@@ -2111,51 +2111,51 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>SHADOW CITY</x:v>
+        <x:v>HELLFORGE</x:v>
       </x:c>
       <x:c r="D42" t="n">
         <x:v>2994</x:v>
       </x:c>
       <x:c r="E42" t="n">
-        <x:v>2385.204081633</x:v>
+        <x:v>2200.180342651037</x:v>
       </x:c>
       <x:c r="F42"/>
       <x:c r="G42" t="n">
-        <x:v>0.13934949</x:v>
+        <x:v>0.1406672678088368</x:v>
       </x:c>
       <x:c r="H42" t="n">
-        <x:v>0.089285714</x:v>
+        <x:v>0.10009017132551848</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:v>696.74744898</x:v>
+        <x:v>811.5419296663661</x:v>
       </x:c>
       <x:c r="J42" t="n">
-        <x:v>1037.946428571</x:v>
+        <x:v>1190.2614968440034</x:v>
       </x:c>
       <x:c r="K42" t="n">
-        <x:v>1551.339285714</x:v>
+        <x:v>1519.3868349864742</x:v>
       </x:c>
       <x:c r="L42" t="n">
-        <x:v>233099.489795918</x:v>
+        <x:v>196798.91794409376</x:v>
       </x:c>
       <x:c r="M42" t="n">
-        <x:v>353954.081632653</x:v>
+        <x:v>308836.78990081156</x:v>
       </x:c>
       <x:c r="N42" t="n">
-        <x:v>385841.836734694</x:v>
+        <x:v>340396.75383228133</x:v>
       </x:c>
       <x:c r="O42" t="n">
-        <x:v>342793.367346939</x:v>
+        <x:v>358431.01893597835</x:v>
       </x:c>
       <x:c r="P42"/>
       <x:c r="Q42" t="n">
-        <x:v>1.061862245</x:v>
+        <x:v>1.0414788097385033</x:v>
       </x:c>
       <x:c r="R42" t="n">
-        <x:v>0.372767857</x:v>
+        <x:v>0.4008115419296664</x:v>
       </x:c>
       <x:c r="S42" t="n">
-        <x:v>3364.158163265</x:v>
+        <x:v>3742.1100090171326</x:v>
       </x:c>
       <x:c r="T42"/>
       <x:c r="U42"/>
@@ -2168,51 +2168,51 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>SHUTEN DOJI/KASAMBO</x:v>
+        <x:v>SHADOW CITY</x:v>
       </x:c>
       <x:c r="D43" t="n">
-        <x:v>239</x:v>
+        <x:v>2994</x:v>
       </x:c>
       <x:c r="E43" t="n">
-        <x:v>2293.59980966</x:v>
+        <x:v>2385.204081632653</x:v>
       </x:c>
       <x:c r="F43"/>
       <x:c r="G43" t="n">
-        <x:v>0.140137997</x:v>
+        <x:v>0.13934948979591838</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>0.090411611</x:v>
+        <x:v>0.08928571428571429</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:v>858.910302165</x:v>
+        <x:v>696.7474489795919</x:v>
       </x:c>
       <x:c r="J43" t="n">
-        <x:v>1084.939329051</x:v>
+        <x:v>1037.9464285714287</x:v>
       </x:c>
       <x:c r="K43" t="n">
-        <x:v>1401.37996669</x:v>
+        <x:v>1551.3392857142858</x:v>
       </x:c>
       <x:c r="L43" t="n">
-        <x:v>198429.693076374</x:v>
+        <x:v>233099.48979591837</x:v>
       </x:c>
       <x:c r="M43" t="n">
-        <x:v>387818.225077326</x:v>
+        <x:v>353954.0816326531</x:v>
       </x:c>
       <x:c r="N43" t="n">
-        <x:v>324768.022840828</x:v>
+        <x:v>385841.83673469385</x:v>
       </x:c>
       <x:c r="O43" t="n">
-        <x:v>360456.8165596</x:v>
+        <x:v>342793.36734693876</x:v>
       </x:c>
       <x:c r="P43"/>
       <x:c r="Q43" t="n">
-        <x:v>1.013561742</x:v>
+        <x:v>1.0618622448979593</x:v>
       </x:c>
       <x:c r="R43" t="n">
-        <x:v>0.423031168</x:v>
+        <x:v>0.37276785714285715</x:v>
       </x:c>
       <x:c r="S43" t="n">
-        <x:v>3271.472757554</x:v>
+        <x:v>3364.158163265306</x:v>
       </x:c>
       <x:c r="T43"/>
       <x:c r="U43"/>
@@ -2225,51 +2225,51 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>TAOTIE/NIU MO</x:v>
+        <x:v>SHUTEN DOJI/KASAMBO</x:v>
       </x:c>
       <x:c r="D44" t="n">
         <x:v>239</x:v>
       </x:c>
       <x:c r="E44" t="n">
-        <x:v>2290.314204103</x:v>
+        <x:v>2293.599809659767</x:v>
       </x:c>
       <x:c r="F44"/>
       <x:c r="G44" t="n">
-        <x:v>0.137886263</x:v>
+        <x:v>0.14013799666904592</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>0.092369329</x:v>
+        <x:v>0.09041161075422317</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:v>828.912712839</x:v>
+        <x:v>858.9103021651201</x:v>
       </x:c>
       <x:c r="J44" t="n">
-        <x:v>1067.255258374</x:v>
+        <x:v>1084.939329050678</x:v>
       </x:c>
       <x:c r="K44" t="n">
-        <x:v>1440.813146864</x:v>
+        <x:v>1401.3799666904592</x:v>
       </x:c>
       <x:c r="L44" t="n">
-        <x:v>205493.934785028</x:v>
+        <x:v>198429.693076374</x:v>
       </x:c>
       <x:c r="M44" t="n">
-        <x:v>372815.966168342</x:v>
+        <x:v>387818.2250773257</x:v>
       </x:c>
       <x:c r="N44" t="n">
-        <x:v>353711.466409467</x:v>
+        <x:v>324768.022840828</x:v>
       </x:c>
       <x:c r="O44" t="n">
-        <x:v>366880.587602478</x:v>
+        <x:v>360456.81655960024</x:v>
       </x:c>
       <x:c r="P44"/>
       <x:c r="Q44" t="n">
-        <x:v>1.027191453</x:v>
+        <x:v>1.0135617416131335</x:v>
       </x:c>
       <x:c r="R44" t="n">
-        <x:v>0.392105947</x:v>
+        <x:v>0.4230311682131811</x:v>
       </x:c>
       <x:c r="S44" t="n">
-        <x:v>3425.826315985</x:v>
+        <x:v>3271.472757554128</x:v>
       </x:c>
       <x:c r="T44"/>
       <x:c r="U44"/>
@@ -2282,43 +2282,53 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>CHIMERA</x:v>
+        <x:v>TAOTIE/NIU MO</x:v>
       </x:c>
       <x:c r="D45" t="n">
-        <x:v>561</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E45" t="n">
-        <x:v>288.368983957</x:v>
-      </x:c>
-      <x:c r="F45" t="n">
-        <x:v>311.631016043</x:v>
-      </x:c>
-      <x:c r="G45"/>
-      <x:c r="H45"/>
+        <x:v>2290.3142041028304</x:v>
+      </x:c>
+      <x:c r="F45"/>
+      <x:c r="G45" t="n">
+        <x:v>0.13788626330823162</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>0.0923693289312609</x:v>
+      </x:c>
       <x:c r="I45" t="n">
-        <x:v>47.895721925</x:v>
+        <x:v>828.9127128389657</x:v>
       </x:c>
       <x:c r="J45" t="n">
-        <x:v>68.390374332</x:v>
+        <x:v>1067.2552583744482</x:v>
       </x:c>
       <x:c r="K45" t="n">
-        <x:v>871.069518717</x:v>
+        <x:v>1440.8131468635233</x:v>
       </x:c>
       <x:c r="L45" t="n">
-        <x:v>228074.86631016</x:v>
-      </x:c>
-      <x:c r="M45"/>
-      <x:c r="N45"/>
-      <x:c r="O45"/>
+        <x:v>205493.934785028</x:v>
+      </x:c>
+      <x:c r="M45" t="n">
+        <x:v>372815.96616834216</x:v>
+      </x:c>
+      <x:c r="N45" t="n">
+        <x:v>353711.4664094669</x:v>
+      </x:c>
+      <x:c r="O45" t="n">
+        <x:v>366880.58760247804</x:v>
+      </x:c>
       <x:c r="P45"/>
-      <x:c r="Q45"/>
-      <x:c r="R45"/>
+      <x:c r="Q45" t="n">
+        <x:v>1.0271914530548651</x:v>
+      </x:c>
+      <x:c r="R45" t="n">
+        <x:v>0.39210594650740066</x:v>
+      </x:c>
       <x:c r="S45" t="n">
-        <x:v>274.812834225</x:v>
-      </x:c>
-      <x:c r="T45" t="n">
-        <x:v>0.097593583</x:v>
-      </x:c>
+        <x:v>3425.8263159847165</x:v>
+      </x:c>
+      <x:c r="T45"/>
       <x:c r="U45"/>
     </x:row>
     <x:row r="46">
@@ -2329,30 +2339,30 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>FENRIR</x:v>
+        <x:v>CHIMERA</x:v>
       </x:c>
       <x:c r="D46" t="n">
         <x:v>561</x:v>
       </x:c>
       <x:c r="E46" t="n">
-        <x:v>277.143615609</x:v>
+        <x:v>288.36898395721926</x:v>
       </x:c>
       <x:c r="F46" t="n">
-        <x:v>309.79559331</x:v>
+        <x:v>311.63101604278074</x:v>
       </x:c>
       <x:c r="G46"/>
       <x:c r="H46"/>
       <x:c r="I46" t="n">
-        <x:v>46.493230688</x:v>
+        <x:v>47.89572192513369</x:v>
       </x:c>
       <x:c r="J46" t="n">
-        <x:v>75.675603929</x:v>
+        <x:v>68.3903743315508</x:v>
       </x:c>
       <x:c r="K46" t="n">
-        <x:v>848.619591187</x:v>
+        <x:v>871.0695187165776</x:v>
       </x:c>
       <x:c r="L46" t="n">
-        <x:v>225378.285107513</x:v>
+        <x:v>228074.86631016043</x:v>
       </x:c>
       <x:c r="M46"/>
       <x:c r="N46"/>
@@ -2361,10 +2371,10 @@
       <x:c r="Q46"/>
       <x:c r="R46"/>
       <x:c r="S46" t="n">
-        <x:v>259.941598089</x:v>
+        <x:v>274.81283422459893</x:v>
       </x:c>
       <x:c r="T46" t="n">
-        <x:v>0.102468808</x:v>
+        <x:v>0.09759358288770054</x:v>
       </x:c>
       <x:c r="U46"/>
     </x:row>
@@ -2376,30 +2386,30 @@
         <x:v>EPIC</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>JORMUNGANDR</x:v>
+        <x:v>FENRIR</x:v>
       </x:c>
       <x:c r="D47" t="n">
         <x:v>561</x:v>
       </x:c>
       <x:c r="E47" t="n">
-        <x:v>283.647798742</x:v>
+        <x:v>277.1436156092381</x:v>
       </x:c>
       <x:c r="F47" t="n">
-        <x:v>346.540880503</x:v>
+        <x:v>309.7955933103265</x:v>
       </x:c>
       <x:c r="G47"/>
       <x:c r="H47"/>
       <x:c r="I47" t="n">
-        <x:v>45.874213836</x:v>
+        <x:v>46.493230687549776</x:v>
       </x:c>
       <x:c r="J47" t="n">
-        <x:v>74.884696017</x:v>
+        <x:v>75.67560392885585</x:v>
       </x:c>
       <x:c r="K47" t="n">
-        <x:v>825.324947589</x:v>
+        <x:v>848.6195911866207</x:v>
       </x:c>
       <x:c r="L47" t="n">
-        <x:v>213836.477987421</x:v>
+        <x:v>225378.2851075126</x:v>
       </x:c>
       <x:c r="M47"/>
       <x:c r="N47"/>
@@ -2408,12 +2418,59 @@
       <x:c r="Q47"/>
       <x:c r="R47"/>
       <x:c r="S47" t="n">
-        <x:v>255.597484277</x:v>
+        <x:v>259.9415980886647</x:v>
       </x:c>
       <x:c r="T47" t="n">
-        <x:v>0.109853249</x:v>
+        <x:v>0.1024688080700823</x:v>
       </x:c>
       <x:c r="U47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>c47</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>EPIC</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>JORMUNGANDR</x:v>
+      </x:c>
+      <x:c r="D48" t="n">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="E48" t="n">
+        <x:v>283.6477987421384</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>346.54088050314465</x:v>
+      </x:c>
+      <x:c r="G48"/>
+      <x:c r="H48"/>
+      <x:c r="I48" t="n">
+        <x:v>45.874213836477985</x:v>
+      </x:c>
+      <x:c r="J48" t="n">
+        <x:v>74.88469601677149</x:v>
+      </x:c>
+      <x:c r="K48" t="n">
+        <x:v>825.3249475890985</x:v>
+      </x:c>
+      <x:c r="L48" t="n">
+        <x:v>213836.4779874214</x:v>
+      </x:c>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
+      <x:c r="Q48"/>
+      <x:c r="R48"/>
+      <x:c r="S48" t="n">
+        <x:v>255.59748427672955</x:v>
+      </x:c>
+      <x:c r="T48" t="n">
+        <x:v>0.10985324947589098</x:v>
+      </x:c>
+      <x:c r="U48"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
